--- a/reportes/Reporte_Inscriptores.xlsx
+++ b/reportes/Reporte_Inscriptores.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="25">
   <si>
     <t>ID</t>
   </si>
@@ -63,6 +63,21 @@
   </si>
   <si>
     <t>Masculino</t>
+  </si>
+  <si>
+    <t>Estados Unidos</t>
+  </si>
+  <si>
+    <t>Perú</t>
+  </si>
+  <si>
+    <t>prueba2@gmail.com</t>
+  </si>
+  <si>
+    <t>Blockchain, Desarrollo Móvil</t>
+  </si>
+  <si>
+    <t>aa</t>
   </si>
   <si>
     <t>Argentina</t>
@@ -414,7 +429,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -457,7 +472,7 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -478,19 +493,57 @@
         <v>16</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J2">
         <v>63212343</v>
       </c>
       <c r="K2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L2" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3">
+        <v>63212343</v>
+      </c>
+      <c r="K3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
